--- a/classes-import.xlsx
+++ b/classes-import.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Work\qr-exams-system\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\MY_WORK\peter\qr-exams-system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5787733-09E7-4FD3-B77C-55B7FE9EADE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A35121-4BD4-4393-B133-5636C2AF7743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="8">
   <si>
     <t>id</t>
   </si>
@@ -42,41 +42,20 @@
     <t>taks_level</t>
   </si>
   <si>
-    <t>1-1-1</t>
-  </si>
-  <si>
-    <t>1-1-2</t>
-  </si>
-  <si>
-    <t>1-1-3</t>
-  </si>
-  <si>
-    <t>1-1-4</t>
-  </si>
-  <si>
-    <t>1-1-5</t>
-  </si>
-  <si>
-    <t>1-1-6</t>
-  </si>
-  <si>
-    <t>1-1-7</t>
-  </si>
-  <si>
-    <t>1-1-8</t>
-  </si>
-  <si>
-    <t>1-1-9</t>
-  </si>
-  <si>
-    <t>1-1-10</t>
+    <t>131-132-133</t>
+  </si>
+  <si>
+    <t>211-212</t>
+  </si>
+  <si>
+    <t>221-222</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,6 +68,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -113,7 +98,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -394,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
@@ -421,179 +408,142 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
+      </c>
+      <c r="B2" s="1">
+        <v>122</v>
+      </c>
+      <c r="C2" s="1">
+        <v>122</v>
+      </c>
+      <c r="D2" s="1">
+        <v>122</v>
+      </c>
+      <c r="E2" s="1">
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
+      </c>
+      <c r="B6" s="1">
+        <v>231</v>
+      </c>
+      <c r="C6" s="1">
+        <v>231</v>
+      </c>
+      <c r="D6" s="1">
+        <v>231</v>
+      </c>
+      <c r="E6" s="1">
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="B7" s="1">
+        <v>311</v>
+      </c>
+      <c r="C7" s="1">
+        <v>311</v>
+      </c>
+      <c r="D7" s="1">
+        <v>311</v>
+      </c>
+      <c r="E7" s="1">
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
+      </c>
+      <c r="B8" s="1">
+        <v>321</v>
+      </c>
+      <c r="C8" s="1">
+        <v>321</v>
+      </c>
+      <c r="D8" s="1">
+        <v>321</v>
+      </c>
+      <c r="E8" s="1">
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
+      </c>
+      <c r="B9" s="1">
+        <v>331</v>
+      </c>
+      <c r="C9" s="1">
+        <v>331</v>
+      </c>
+      <c r="D9" s="1">
+        <v>331</v>
+      </c>
+      <c r="E9" s="1">
+        <v>331</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="B3" twoDigitTextYear="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/classes-import.xlsx
+++ b/classes-import.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\MY_WORK\peter\qr-exams-system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A35121-4BD4-4393-B133-5636C2AF7743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6669C34F-2D1C-466F-A3A0-42DC4356F62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="26">
   <si>
     <t>id</t>
   </si>
@@ -42,20 +42,74 @@
     <t>taks_level</t>
   </si>
   <si>
-    <t>131-132-133</t>
-  </si>
-  <si>
-    <t>211-212</t>
-  </si>
-  <si>
-    <t>221-222</t>
+    <t>011</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>222</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>331</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -68,12 +122,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFCE9178"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -98,9 +146,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -381,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
@@ -408,41 +454,41 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>24</v>
-      </c>
-      <c r="B2" s="1">
-        <v>122</v>
-      </c>
-      <c r="C2" s="1">
-        <v>122</v>
-      </c>
-      <c r="D2" s="1">
-        <v>122</v>
-      </c>
-      <c r="E2" s="1">
-        <v>122</v>
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
@@ -459,87 +505,308 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>28</v>
-      </c>
-      <c r="B6" s="1">
-        <v>231</v>
-      </c>
-      <c r="C6" s="1">
-        <v>231</v>
-      </c>
-      <c r="D6" s="1">
-        <v>231</v>
-      </c>
-      <c r="E6" s="1">
-        <v>231</v>
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>29</v>
-      </c>
-      <c r="B7" s="1">
-        <v>311</v>
-      </c>
-      <c r="C7" s="1">
-        <v>311</v>
-      </c>
-      <c r="D7" s="1">
-        <v>311</v>
-      </c>
-      <c r="E7" s="1">
-        <v>311</v>
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>30</v>
-      </c>
-      <c r="B8" s="1">
-        <v>321</v>
-      </c>
-      <c r="C8" s="1">
-        <v>321</v>
-      </c>
-      <c r="D8" s="1">
-        <v>321</v>
-      </c>
-      <c r="E8" s="1">
-        <v>321</v>
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>31</v>
-      </c>
-      <c r="B9" s="1">
-        <v>331</v>
-      </c>
-      <c r="C9" s="1">
-        <v>331</v>
-      </c>
-      <c r="D9" s="1">
-        <v>331</v>
-      </c>
-      <c r="E9" s="1">
-        <v>331</v>
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/classes-import.xlsx
+++ b/classes-import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\MY_WORK\peter\qr-exams-system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6669C34F-2D1C-466F-A3A0-42DC4356F62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C07CFD-CE00-4248-99D7-7E6FB0590261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17808" yWindow="3000" windowWidth="2472" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
